--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_461_Malaysia_Sabah.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_461_Malaysia_Sabah.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Racccbb331b104078"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4c6187adc5244e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rde037043aaab4ff5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rab8de4be4df246fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra09f80ba6d9b48c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1439e3e82b904dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Raa20cfe2f63141f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd01b302f32954e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rceead935ef214dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6532d3f87c8e422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R618415849e6f4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re0650f29e0e64eb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ461CommercialTable" displayName="EEZ461CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ461CommercialTable" displayName="EEZ461CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ461FunctionalTable" displayName="EEZ461FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ461FunctionalTable" displayName="EEZ461FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ461ValidationTable" displayName="EEZ461ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ461ValidationTable" displayName="EEZ461ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8332,7 +8286,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e05568beb14c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f31abea3194ce2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8342,20 +8296,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8363,606 +8307,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>349.89919578129997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>349.89919578129997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$115,A2,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>55455.285344140095</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>55455.285344140095</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>36118.8219302437</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.155689969118687</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>143.1165864582555</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>36118.8219302437</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>314.6757060701983</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$115,A3,'Species'!$U$2:$U$115))</x:f>
-        <x:v>11365715.7933232</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.155689969118687</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>143.1165864582555</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5169202.501550058</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>6196513.291773142</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>2.198736805129037</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.198736805129037</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1806.4504319782</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.648256233908203</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>444.8936774880891</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1806.4504319782</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>495.79436806560307</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$115,A4,'Species'!$U$2:$U$115))</x:f>
-        <x:v>895627.9503644673</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.648256233908203</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>444.8936774880891</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>803678.3758827285</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>91949.57448173885</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.114410910186236</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.11441091018623598</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>38539.74419471601</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.03692482205267</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>108.87416119053107</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>38539.74419471601</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>142.4116079284371</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$115,A5,'Species'!$U$2:$U$115))</x:f>
-        <x:v>5488506.939920156</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.03692482205267</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>108.87416119053107</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4195982.321697345</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1292524.6182228113</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.308038623408681</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.30803862340868093</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1507.4631475059998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0979803485056485</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.530844725410875</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1507.4631475059998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.536960208456115</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$115,A6,'Species'!$U$2:$U$115))</x:f>
-        <x:v>18899.00549599673</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0979803485056485</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.530844725410875</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>18889.786630676834</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9.218865319897304</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.000488034380702</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00048803438070210676</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>108892.7938383891</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.358322684325254</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>228.2037014269573</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>108892.7938383891</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>266.04457803952545</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$115,A7,'Species'!$U$2:$U$115))</x:f>
-        <x:v>28970337.388279267</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.358322684325254</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>228.2037014269573</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>24849738.612642962</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4120598.775636304</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1658206084123492</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16582060841234927</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>282323.2117226735</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.879397703794572</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>757.5262797785186</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>282323.2117226735</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1341.158654576546</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$115,A8,'Species'!$U$2:$U$115))</x:f>
-        <x:v>378640218.78971016</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.879397703794572</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>757.5262797785186</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>213867252.27139992</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>164772966.51831025</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7704450530332316</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7704450530332317</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1725.3308994791</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1725.3308994791</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$115,A9,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1370479.0476984899</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>1370479.0476984899</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13398.2049663918</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.093026335434158</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1238.8717089104114</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13398.2049663918</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1366.4707202358077</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$115,A10,'Species'!$U$2:$U$115))</x:f>
-        <x:v>18308254.79029238</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.093026335434158</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1238.8717089104114</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>16598657.083045771</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1709597.7072466072</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1029961459347712</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10299614593477127</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5897.036937722</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.499385355641491</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3157.805346014588</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5897.036937722</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3158.1640568273956</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$115,A11,'Species'!$U$2:$U$115))</x:f>
-        <x:v>18623810.098497115</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.499385355641491</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3157.805346014588</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>18621694.767584026</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2115.3309130892158</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000113594972933</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00011359497293294204</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa2346107534367"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e7ae52b0ca64100"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8972,20 +8522,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8993,1146 +8533,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>207.2091974742</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7134918530600745</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>517.00155943384</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>207.2091974742</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>553.3845678683692</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$115,A2,'Species'!$U$2:$U$115))</x:f>
-        <x:v>114666.37220261175</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7134918530600745</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>517.00155943384</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>107127.47822319591</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7538.893979415836</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0703731115905561</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07037311159055612</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6436.9526780122005</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4600000000000004</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266084</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6436.9526780122005</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$115,A3,'Species'!$U$2:$U$115))</x:f>
-        <x:v>1856437.4307522355</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4600000000000004</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266084</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1856437.4307522373</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-1.862645149230957e-9</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-1.003343887801381e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5465.7915258349</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.198902984373238</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1580.8948488826263</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5465.7915258349</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1632.9877289600322</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$115,A4,'Species'!$U$2:$U$115))</x:f>
-        <x:v>8925570.490742123</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.198902984373238</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1580.8948488826263</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>8640841.668258704</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>284728.8224834185</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0329515148425115</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0329515148425115</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>11117.8895649711</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.268060382438327</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1853.7893484020126</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>11117.8895649711</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1951.6070654405448</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$115,A5,'Species'!$U$2:$U$115))</x:f>
-        <x:v>21697751.827785302</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.268060382438327</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1853.7893484020126</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>20610225.25225331</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1087526.575531993</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0527663604944393</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.052766360494439245</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>53936.0911023714</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.357895897049288</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2279.7955260539266</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>53936.0911023714</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2315.1830392602405</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$115,A6,'Species'!$U$2:$U$115))</x:f>
-        <x:v>124871923.32420543</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.357895897049288</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2279.7955260539266</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>122963259.18802331</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1908664.1361821145</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0155222311834105</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01552223118341043</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5429.691332383</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8499542562751823</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>707.8712212177436</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5429.691332383</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>707.8813426218088</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$115,A7,'Species'!$U$2:$U$115))</x:f>
-        <x:v>3843577.1903892765</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8499542562751823</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>707.8712212177436</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3843522.234289352</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>54.95609992463142</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000142983691975</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000014298369197490157</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5502.9464778529</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9599883300099576</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>911.9863329095659</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5502.9464778529</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1028.851825943153</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$115,A8,'Species'!$U$2:$U$115))</x:f>
-        <x:v>5661716.531806398</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9599883300099576</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>911.9863329095659</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5018611.978534678</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>643104.5532717202</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1281439083201432</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1281439083201432</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>7968.5136340088</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.258654007290175</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1814.0698580072624</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>7968.5136340088</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1815.229070848212</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$115,A9,'Species'!$U$2:$U$115))</x:f>
-        <x:v>14464677.599903103</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.258654007290175</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1814.0698580072624</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14455440.396575278</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9237.203327825293</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0006390122386042</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0006390122386042097</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13888.532837835999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.4841258885562105</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>30.4877860830556</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13888.532837835999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>30.66294986477633</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$115,A10,'Species'!$U$2:$U$115))</x:f>
-        <x:v>425863.386101865</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.4841258885562105</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>30.4877860830556</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>423430.6181674371</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2432.7679344278877</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.005745375582325</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005745375582324797</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>13621.5157644326</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4192262045287034</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>262.5585737219173</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>13621.5157644326</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>354.6378670508571</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$115,A11,'Species'!$U$2:$U$115))</x:f>
-        <x:v>4830705.296698002</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4192262045287034</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>262.5585737219173</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3576445.7510400354</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1254259.5456579668</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.3507000058069458</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3507000058069457</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>121907.19161453782</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.324553749904523</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>211.13184842877115</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>121907.19161453782</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>284.5819167858835</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$115,A12,'Species'!$U$2:$U$115))</x:f>
-        <x:v>34692582.25964916</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.324553749904523</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>211.13184842877115</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>25738490.70233776</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8954091.557311397</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3478872036773362</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.34788720367733605</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>43106.3071310901</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.633085517858158</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>429.6210160322539</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>43106.3071310901</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>960.6976859233223</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$115,A13,'Species'!$U$2:$U$115))</x:f>
-        <x:v>41412129.50953826</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.633085517858158</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>429.6210160322539</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>18519375.46705732</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>22892754.04248094</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.236151515109302</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.2361515151093019</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>120211.7768272656</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.9738346134725564</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>941.5309776620275</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>120211.7768272656</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1493.340088440642</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$115,A14,'Species'!$U$2:$U$115))</x:f>
-        <x:v>179517065.4388355</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.9738346134725564</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>941.5309776620275</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>113183111.76266484</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>66333953.67617066</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.586076426448384</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.586076426448384</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1511.3805651069997</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.098840925686982</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.555699865954075</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1511.3805651069997</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.574228220803784</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$115,A15,'Species'!$U$2:$U$115))</x:f>
-        <x:v>19004.444154142806</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.098840925686982</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.555699865954075</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>18976.44075871955</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>28.003395423256734</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0014756927170545</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0014756927170544011</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>22230.289092407704</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.5752544537203983</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>376.05767244993876</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>22230.289092407704</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>492.11471617603104</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$115,A16,'Species'!$U$2:$U$115))</x:f>
-        <x:v>10939852.407221336</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.5752544537203983</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>376.05767244993876</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>8359870.7739801025</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2579981.6332412334</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.3086150136759727</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.30861501367597266</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>12470.060428168601</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2334071545544725</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>171.16192198607357</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>12470.060428168601</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>171.4630509858608</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$115,A17,'Species'!$U$2:$U$115))</x:f>
-        <x:v>2138154.606991838</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2334071545544725</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>171.16192198607357</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2134399.510167817</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3755.0968240210786</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0017593223790264</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0017593223790263305</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4752.815408868601</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.612356989518063</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>409.59720978063314</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4752.815408868601</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>421.65954890175675</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$115,A18,'Species'!$U$2:$U$115))</x:f>
-        <x:v>2004070.0013168526</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.612356989518063</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>409.59720978063314</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1946739.930074978</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>57330.07124187471</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0294492707301004</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.029449270730100383</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>38904.472645910304</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.0362722183623108</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>108.7106815119819</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>38904.472645910304</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>138.8614042998288</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$115,A19,'Species'!$U$2:$U$115))</x:f>
-        <x:v>5402329.705155381</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.0362722183623108</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>108.7106815119819</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>4229331.735201167</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1172997.969954214</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2773483007235469</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.277348300723547</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>83.0790043697</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.4378147572469437</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>274.04050379094383</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>83.0790043697</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>284.0587136449896</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$115,A20,'Species'!$U$2:$U$115))</x:f>
-        <x:v>23599.31511216345</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.4378147572469437</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>274.04050379094383</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>22767.01221192261</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>832.3029002408402</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0365574056223759</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.036557405622375895</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1806.4504319782</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.648256233908203</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>444.8936774880891</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1806.4504319782</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>495.79436806560307</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$115,A21,'Species'!$U$2:$U$115))</x:f>
-        <x:v>895627.9503644673</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.648256233908203</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>444.8936774880891</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>803678.3758827285</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>91949.57448173885</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.114410910186236</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.11441091018623598</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re407ec0bcf13413f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaa5ce64186742df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10307,7 +9103,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10406,7 +9202,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>463737305.0889254</x:v>
+        <x:v>285551030.0534761</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10420,7 +9216,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>463737305.0889255</x:v>
+        <x:v>356452083.706455</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10434,7 +9230,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-178186275.0354494</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10448,7 +9244,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-107285221.38247049</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10459,9 +9255,9 @@
         <x:v>EEZ_461</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10473,47 +9269,19 @@
         <x:v>EEZ_461</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_461</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_461</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013d896e0671440b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa16028ceb3542ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10560,7 +9328,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
